--- a/src/attributions/attributions_ig_traj_317.xlsx
+++ b/src/attributions/attributions_ig_traj_317.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG5"/>
+  <dimension ref="A1:GG9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1002,43 +1002,43 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9993146397459965</v>
+        <v>0.8886991453909695</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1880462314427948</v>
+        <v>-0.5177054104973419</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1714250431640147</v>
+        <v>-0.1537912981959452</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5366890258076726</v>
+        <v>0.6582482541171157</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2191943946599505</v>
+        <v>-0.5336415542124224</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.07531201027041269</v>
+        <v>-0.1855803709347582</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1056,43 +1056,43 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1888242731910357</v>
+        <v>0.1524321193695801</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.03491220716361781</v>
+        <v>-0.1020206413870353</v>
       </c>
       <c r="W2" t="n">
-        <v>0.04112688148520702</v>
+        <v>-0.02415553908167124</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>-0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1984389770313054</v>
+        <v>-0.03888820913286693</v>
       </c>
       <c r="AD2" t="n">
         <v>-0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.05279817565431985</v>
+        <v>-0.3726597611896252</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.01106948684524994</v>
+        <v>-0.01053319940015164</v>
       </c>
       <c r="AG2" t="n">
         <v>-0</v>
@@ -1104,22 +1104,22 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.1098843790816191</v>
+        <v>0.2213241677352945</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.07115234988343493</v>
+        <v>-0.2249272391167804</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.04319062428223332</v>
+        <v>0.2342876399540633</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
@@ -1128,52 +1128,52 @@
         <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT2" t="n">
         <v>-0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.4976472599148012</v>
+        <v>0.5047074576311591</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.004249993027951406</v>
+        <v>-0.3527120187342849</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.02022327219701178</v>
+        <v>-0.2591055633554007</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.1784002967574037</v>
+        <v>0.1124874958020754</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.09387079741627639</v>
+        <v>-0.1056357954000342</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.2551693714716207</v>
+        <v>0.02252048709944958</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1182,31 +1182,31 @@
         <v>-0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
         <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.03606928234421171</v>
+        <v>-0.1259963389239786</v>
       </c>
       <c r="BN2" t="n">
         <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.04869759727457275</v>
+        <v>0.009854656710245909</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.121066711482997</v>
+        <v>0.09015462830222851</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
         <v>-0</v>
@@ -1218,22 +1218,22 @@
         <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.3441128736294349</v>
+        <v>0.4606706436585328</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0.04233260628690172</v>
+        <v>-0.2891617175485794</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.09480287950832175</v>
+        <v>-0.05025577777149227</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB2" t="n">
         <v>0</v>
@@ -1245,97 +1245,97 @@
         <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.1913896341370187</v>
+        <v>-0.3067539562974024</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.04101898848135863</v>
+        <v>0.2764699301624012</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.01847273611422675</v>
+        <v>0.02747720997584527</v>
       </c>
       <c r="CI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.03582741816708116</v>
+        <v>-0.3362189327444084</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.05058190521671795</v>
+        <v>0.5818959513815433</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.1953715550215852</v>
+        <v>-0.0003789290101399289</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT2" t="n">
         <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.2008362644533669</v>
+        <v>-0.2832116710287322</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.04901358994275447</v>
+        <v>0.2813441497425087</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.02762724467243059</v>
+        <v>0.02399882157383708</v>
       </c>
       <c r="DA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.07434312797320351</v>
+        <v>-0.06701056156564925</v>
       </c>
       <c r="DG2" t="n">
         <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.09223395592440012</v>
+        <v>0.1173029350477493</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.1250492300792749</v>
+        <v>0.00835336398833365</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
@@ -1344,25 +1344,25 @@
         <v>-0</v>
       </c>
       <c r="DL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
         <v>0</v>
       </c>
       <c r="DN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.07051490117378462</v>
+        <v>-0.04102011262346375</v>
       </c>
       <c r="DP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0.05142581736891507</v>
+        <v>0.1059052996817814</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.0982896079908889</v>
+        <v>0.03430515328210595</v>
       </c>
       <c r="DS2" t="n">
         <v>-0</v>
@@ -1371,160 +1371,160 @@
         <v>-0</v>
       </c>
       <c r="DU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV2" t="n">
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.1251855303992438</v>
+        <v>0.1898612841217906</v>
       </c>
       <c r="DY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.08669311122127062</v>
+        <v>-0.2017103297806994</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.05984278336463478</v>
+        <v>-0.03126183022430833</v>
       </c>
       <c r="EB2" t="n">
         <v>0</v>
       </c>
       <c r="EC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED2" t="n">
         <v>0</v>
       </c>
       <c r="EE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.1672205814717104</v>
+        <v>-0.315754058196264</v>
       </c>
       <c r="EH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.022267092239796</v>
+        <v>0.2378548713412661</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.1371682097412814</v>
+        <v>-0.1954604976343761</v>
       </c>
       <c r="EK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN2" t="n">
         <v>-0</v>
       </c>
       <c r="EO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.1569381228313191</v>
+        <v>-0.1050541527855969</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.001537572724283855</v>
+        <v>0.1586558473205964</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.03521338411668703</v>
+        <v>-0.09098110178877251</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.2092833722392584</v>
+        <v>-0.3411723142839234</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.03623380786992013</v>
+        <v>0.3330762090414524</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.02575549347593614</v>
+        <v>0.0009699981954183532</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
         <v>0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.03598082912731602</v>
+        <v>-0.1800179623494168</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.06632099893233542</v>
+        <v>0.1213250118775491</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.1242884529974941</v>
+        <v>-0.0949182109156506</v>
       </c>
       <c r="FL2" t="n">
         <v>-0</v>
       </c>
       <c r="FM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN2" t="n">
         <v>-0</v>
       </c>
       <c r="FO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.1142121185414288</v>
+        <v>-0.343951084531646</v>
       </c>
       <c r="FR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.1298101951319458</v>
+        <v>0.3141808983994772</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.04603239838852444</v>
+        <v>0.3972393613623529</v>
       </c>
       <c r="FU2" t="n">
         <v>-0</v>
@@ -1539,28 +1539,28 @@
         <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.07575575644486716</v>
+        <v>-0.2754220909760396</v>
       </c>
       <c r="GA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB2" t="n">
-        <v>-0.07378646165408284</v>
+        <v>0.2293307798149866</v>
       </c>
       <c r="GC2" t="n">
         <v>0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG2" t="n">
         <v>-0</v>
@@ -2706,46 +2706,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.7086594723034525</v>
+        <v>0.2589801432613751</v>
       </c>
       <c r="C5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8410089076440637</v>
+        <v>-0.4492945941707455</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02998871231035606</v>
+        <v>0.1292678955203409</v>
       </c>
       <c r="F5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4721760938508761</v>
+        <v>0.1647456731383448</v>
       </c>
       <c r="L5" t="n">
         <v>-0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7859504362087734</v>
+        <v>-0.6690406308984868</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07745248670353802</v>
+        <v>-0.01025125813769675</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
         <v>-0</v>
       </c>
       <c r="R5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.179798170957105</v>
+        <v>0.01816881049610389</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.05759577494294525</v>
+        <v>0.004263819852843331</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.02080037281984061</v>
+        <v>-0.04298602732289294</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -2784,22 +2784,22 @@
         <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.1163377017285103</v>
+        <v>0.01248488990615879</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.103663730896983</v>
+        <v>-0.1543243481382098</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.05517537346936537</v>
+        <v>0.01834423179670026</v>
       </c>
       <c r="AG5" t="n">
         <v>-0</v>
@@ -2808,52 +2808,52 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.09845066088063925</v>
+        <v>0.1455349639430031</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.08105785337520885</v>
+        <v>-0.05094596524530004</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.05602075002332013</v>
+        <v>0.05748998251513009</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
         <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.3714139687205934</v>
+        <v>0.148668058963102</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.2475305694754233</v>
+        <v>-0.2274576664036257</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.1312931321743758</v>
+        <v>-0.2173195147907228</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
@@ -2862,31 +2862,31 @@
         <v>-0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB5" t="n">
         <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.1914014938082297</v>
+        <v>2.382857050097373e-05</v>
       </c>
       <c r="BE5" t="n">
         <v>-0</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.3263472640836555</v>
+        <v>-0.1737655392196014</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.2145669197705451</v>
+        <v>0.07440161271386853</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
@@ -2895,46 +2895,46 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.08694538615607267</v>
+        <v>-0.04517250411251487</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.0911658867593326</v>
+        <v>-0.009521891360671166</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.1654673572237439</v>
+        <v>-0.004978683319358298</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.2430543190070406</v>
+        <v>0.1387138374383485</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.1433882155440886</v>
+        <v>-0.1423169012776314</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.1703754647986475</v>
+        <v>-0.04270752540080059</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -2946,22 +2946,22 @@
         <v>-0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.1211107417633771</v>
+        <v>-0.08138965662792691</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.139253349517886</v>
+        <v>0.1450626001600182</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.02181038568039272</v>
+        <v>-0.01379207513546309</v>
       </c>
       <c r="CI5" t="n">
         <v>-0</v>
@@ -2973,31 +2973,31 @@
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.0162251149026494</v>
+        <v>0.06937519473971102</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.03171846659019248</v>
+        <v>0.2560313167736371</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.07942009121021622</v>
+        <v>0.1996596657212049</v>
       </c>
       <c r="CR5" t="n">
         <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU5" t="n">
         <v>-0</v>
@@ -3006,19 +3006,19 @@
         <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.1330547574140201</v>
+        <v>-0.0700168333981062</v>
       </c>
       <c r="CX5" t="n">
         <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.1319279106146896</v>
+        <v>0.1495019282796382</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.01139896722554616</v>
+        <v>0.01015618867636267</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
         <v>-0</v>
@@ -3030,46 +3030,46 @@
         <v>-0</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.1241514564115869</v>
+        <v>0.002926217441348467</v>
       </c>
       <c r="DG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.00867865820231801</v>
+        <v>-0.005152553160865181</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.06568360544515235</v>
+        <v>-0.08533072610681919</v>
       </c>
       <c r="DJ5" t="n">
         <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
         <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.02822475013098412</v>
+        <v>-0.1243555841149316</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.02765372593053477</v>
+        <v>0.005390532508821631</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.02766153163433772</v>
+        <v>-0.02629219631551514</v>
       </c>
       <c r="DS5" t="n">
         <v>-0</v>
@@ -3078,31 +3078,31 @@
         <v>0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.1159772034595191</v>
+        <v>0.1400074878065872</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.1285753115955622</v>
+        <v>-0.01378673924250635</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0323268712170375</v>
+        <v>0.02473811566863388</v>
       </c>
       <c r="EB5" t="n">
         <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED5" t="n">
         <v>-0</v>
@@ -3111,22 +3111,22 @@
         <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.1079628634547527</v>
+        <v>-0.1186203011830205</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.1008079824337839</v>
+        <v>0.1392664250530405</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.03988600520052032</v>
+        <v>-0.04695872771669665</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
         <v>0</v>
@@ -3135,25 +3135,25 @@
         <v>0</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.1394698652668503</v>
+        <v>0.1460045347818665</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.09681132118085786</v>
+        <v>0.1887040051586275</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.06300273849657879</v>
+        <v>-0.02676013496369029</v>
       </c>
       <c r="ET5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU5" t="n">
         <v>0</v>
@@ -3162,76 +3162,76 @@
         <v>0</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX5" t="n">
         <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.1387827793844546</v>
+        <v>-0.1050799122991442</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>-0.1342304359846084</v>
+        <v>0.147192689558918</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.02042269461083275</v>
+        <v>-0.03642590372392851</v>
       </c>
       <c r="FC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD5" t="n">
         <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG5" t="n">
         <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.003740589465110174</v>
+        <v>0.01716204016852636</v>
       </c>
       <c r="FI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.02649977301801416</v>
+        <v>0.0575996536500265</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.08905933153277301</v>
+        <v>-0.08368667619936528</v>
       </c>
       <c r="FL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.01666214158722958</v>
+        <v>0.0363106237595819</v>
       </c>
       <c r="FR5" t="n">
         <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>-0.04153370833229746</v>
+        <v>-0.05941364125332297</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.04620107886425804</v>
+        <v>0.01364516247788491</v>
       </c>
       <c r="FU5" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
         <v>-0</v>
@@ -3249,13 +3249,13 @@
         <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.01489701682633079</v>
+        <v>0.001620736411216665</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.06676956604522326</v>
+        <v>0.02286313688071825</v>
       </c>
       <c r="GC5" t="n">
         <v>-0</v>
@@ -3264,12 +3264,2288 @@
         <v>0</v>
       </c>
       <c r="GE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF5" t="n">
         <v>-0</v>
       </c>
       <c r="GG5" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.2516066825064371</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.01797265313601219</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2375769544437332</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.2002169209096735</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.08477923838814752</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1273169493916664</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.04382595773003819</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.03042722095716804</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.1086718631612437</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.03855910365995924</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.0294862275872924</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-0.02219519747284174</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0.1222416199722303</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-0.1677410976859745</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.08254796349641816</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0.1731924418711259</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.0502481970964295</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.2371199560032149</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.1238796315400257</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0.07149550176177262</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0.009818874145585459</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.06456179282601271</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>-0.03352450720475642</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.007573376625165234</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>-0.1376968163921413</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>-0.05025650152728522</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0.2131567370264415</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.1644005742115679</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.006750101584216599</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>-0.08499503799636335</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0.09535901577882068</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>-0.07988411131197816</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>-0.1806671920166586</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>0.1725535890547295</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>-0.02249824152440163</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>-0.08862078983612399</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>-0.009050207822087406</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>-0.005310853186882894</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>-0.08660094715875941</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>0.05799189331304123</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0.02072038385570585</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>-0.05070810815012745</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>0.09873371469694298</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>0.02792521906474069</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>0.1462792350258402</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>0.1506511609739067</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>-0.02431142588680223</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>-0.001832749705267901</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>-0.0720034543039858</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>0.02144694557227032</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>-0.001534171164239076</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>0.1808351254788266</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>0.005200303702889575</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>-0.1007630587133213</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>0.08602474769719974</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>0.02939573329854254</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>-0.03520014717494755</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>0.1486501864824483</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>0.03599637648278151</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>0.01405211108550683</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>0.171350114942814</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>-0.02692845819520769</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.2576024284448153</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.003381329356720347</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2063663628960547</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.1563191615093105</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.1063064131310672</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.1598091813011858</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.1041197210687528</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1279108829702983</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.007228047947761117</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.03940988960302492</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.1852308334982876</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.06004736502600713</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-0.11233647747022</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.003654273261109488</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.07400207926579405</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-0.4398660489655812</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.1445893296557119</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.1036183754066601</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.03183764390982202</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.09657216136909863</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0.09825513853569283</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>-0.02211332306913739</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>-0.05585008723471344</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.01677951162518161</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>-0.2284656513678524</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0.0831858558297342</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0.07791426055718402</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0.1203937966853453</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>-0.01264927326485775</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>-0.05904355836586375</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0.1588710410014456</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>-0.1965810051201823</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>-0.09884303889077456</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0.1037152095929863</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>-0.006825628307141098</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>-0.06607981041549305</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>0.03425823505538265</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0.1141736305046984</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>-0.007545480700915421</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>0.03834853180858225</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>0.04796700079942275</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>-0.01209894271782174</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>-0.06434710606077398</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0.01347131672418889</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>-0.02023440315917413</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>0.0469004100178524</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>0.03641698626109222</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>-0.03466146297782145</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>0.04393021270025463</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>0.03514146220170652</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>-0.07370156868678387</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>0.1280721345679844</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>0.0005495451448267713</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>-0.05558351741433697</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>0.1022141591778944</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>-0.07880403972695575</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>-0.05889167398131285</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>-0.0246394559820254</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0.003239762133561349</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>-0.07052977591941859</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>0.1048233933288169</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0.01087474826850794</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5180481033177419</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.06147994282379924</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.209093573008236</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.643979264321317</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.07181431967098559</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.1110065846545526</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.0825688503498333</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.06198560141531508</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.04076128392298476</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.01791058539452526</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.1630568678752857</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0.07516107783948249</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.07902847171312587</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.0130707113805475</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.1534995418770378</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.4745401595134287</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-0.223957936144948</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0.1342807609504265</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.006898298446222749</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-0.05945762377877578</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>-0.1059214426079688</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.0813423821057223</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.09997891046611389</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>-0.001708946803609338</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.2973278672917199</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>-0.08465652771461853</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>-0.08813786074675257</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>-0.1509462880393314</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.03739010556203573</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.06568594532480369</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>-0.2408495160815819</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.2585020257848481</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.1242683961836985</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>-0.1537191133321979</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>-0.005172126432719299</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.05930396982316762</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0.002126596608247948</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>-0.0605692745775366</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0.01037031573494669</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>-0.08112097273615204</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>-0.03961490702160498</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>-0.005410691007561073</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.05379098968229609</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>-0.05268054833391958</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>-0.05592312843756012</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>-0.03698881960208775</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>-0.05929001476202606</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0.02433424203969798</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>-0.0693866785405625</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>-0.03800474644069021</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>-0.09810446638067608</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>-0.163350001726733</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>0.007860646053425525</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0.05230941185838079</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>-0.1325234891259381</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>0.07938080095738352</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0.1221670086556265</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>-0.1169374370399837</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>0.01811202582686371</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0.07554990158658766</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>-0.07945850591444292</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>-0.04679376899199307</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG9" t="n">
         <v>0</v>
       </c>
     </row>
